--- a/jpcore-r4b/develop/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="479">
   <si>
     <t>Property</t>
   </si>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -472,14 +472,6 @@
   </si>
   <si>
     <t>関連するEncounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -2981,10 +2973,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -3001,14 +2993,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3030,16 +3022,16 @@
         <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -3088,7 +3080,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3117,10 +3109,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3143,13 +3135,13 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3200,7 +3192,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3215,24 +3207,24 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3258,13 +3250,13 @@
         <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3290,14 +3282,14 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="Y13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
       </c>
@@ -3314,7 +3306,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>90</v>
@@ -3329,24 +3321,24 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>174</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3369,16 +3361,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3428,7 +3420,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3440,13 +3432,13 @@
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
@@ -3457,10 +3449,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3483,13 +3475,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3540,7 +3532,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3558,7 +3550,7 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -3569,14 +3561,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3598,13 +3590,13 @@
         <v>136</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3654,7 +3646,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3672,7 +3664,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -3683,14 +3675,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3712,16 +3704,16 @@
         <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3770,7 +3762,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3799,10 +3791,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3828,13 +3820,13 @@
         <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3860,14 +3852,14 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z18" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="Y18" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
       </c>
@@ -3884,7 +3876,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>90</v>
@@ -3902,7 +3894,7 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>81</v>
@@ -3913,10 +3905,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3939,16 +3931,16 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3998,7 +3990,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>90</v>
@@ -4016,7 +4008,7 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>81</v>
@@ -4027,10 +4019,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4053,16 +4045,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4088,14 +4080,14 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Z20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4112,7 +4104,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>90</v>
@@ -4130,21 +4122,21 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4167,13 +4159,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4224,7 +4216,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4236,13 +4228,13 @@
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
@@ -4253,10 +4245,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4279,13 +4271,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4336,7 +4328,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4354,7 +4346,7 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -4365,14 +4357,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4394,13 +4386,13 @@
         <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4450,7 +4442,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4468,7 +4460,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -4479,14 +4471,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4508,16 +4500,16 @@
         <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4566,7 +4558,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4595,10 +4587,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4621,16 +4613,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4656,14 +4648,14 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y25" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
       </c>
@@ -4680,7 +4672,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>90</v>
@@ -4698,7 +4690,7 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -4709,10 +4701,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4735,16 +4727,16 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4794,7 +4786,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -4812,7 +4804,7 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
@@ -4823,10 +4815,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4849,16 +4841,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4884,14 +4876,14 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Y27" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
       </c>
@@ -4908,7 +4900,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4923,24 +4915,24 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4963,13 +4955,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4996,13 +4988,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -5020,7 +5012,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5035,24 +5027,24 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5075,13 +5067,13 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5108,13 +5100,13 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5132,7 +5124,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5150,25 +5142,25 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5187,16 +5179,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5246,7 +5238,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5261,24 +5253,24 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5301,13 +5293,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5358,7 +5350,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5373,28 +5365,28 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>268</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5413,13 +5405,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5470,7 +5462,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5485,10 +5477,10 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -5499,10 +5491,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5525,13 +5517,13 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5582,7 +5574,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5594,27 +5586,27 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5637,13 +5629,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5694,7 +5686,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5712,7 +5704,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -5723,14 +5715,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5752,13 +5744,13 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5808,7 +5800,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5826,7 +5818,7 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -5837,14 +5829,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5866,16 +5858,16 @@
         <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5924,7 +5916,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5953,10 +5945,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5979,16 +5971,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6014,14 +6006,14 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6038,7 +6030,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6053,24 +6045,24 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6093,13 +6085,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6150,7 +6142,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6168,21 +6160,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6205,13 +6197,13 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6262,7 +6254,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6277,24 +6269,24 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6317,13 +6309,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6374,7 +6366,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6389,24 +6381,24 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6429,16 +6421,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6488,7 +6480,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6503,24 +6495,24 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6543,16 +6535,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6602,7 +6594,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6617,28 +6609,28 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6657,16 +6649,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6695,10 +6687,10 @@
         <v>114</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -6716,7 +6708,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6731,28 +6723,28 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6771,16 +6763,16 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6830,7 +6822,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6845,24 +6837,24 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6885,13 +6877,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6942,7 +6934,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6954,13 +6946,13 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -6971,10 +6963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6997,13 +6989,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7054,7 +7046,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7072,7 +7064,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7083,14 +7075,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7112,13 +7104,13 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7168,7 +7160,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7186,7 +7178,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7197,14 +7189,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7226,16 +7218,16 @@
         <v>136</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7284,7 +7276,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7313,14 +7305,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7339,16 +7331,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L49" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>352</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7398,7 +7390,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7413,24 +7405,24 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7453,13 +7445,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7489,10 +7481,10 @@
         <v>114</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7510,7 +7502,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7528,7 +7520,7 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -7539,10 +7531,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7565,13 +7557,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7622,7 +7614,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7640,7 +7632,7 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
@@ -7651,10 +7643,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7677,16 +7669,16 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7736,7 +7728,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7754,7 +7746,7 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7765,10 +7757,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7791,16 +7783,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7850,7 +7842,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7862,13 +7854,13 @@
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -7879,10 +7871,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7905,13 +7897,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7962,7 +7954,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7980,7 +7972,7 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -7991,14 +7983,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8020,13 +8012,13 @@
         <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8076,7 +8068,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8094,7 +8086,7 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
@@ -8105,14 +8097,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8134,16 +8126,16 @@
         <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8192,7 +8184,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8221,10 +8213,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8247,13 +8239,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8304,7 +8296,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8322,21 +8314,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8359,13 +8351,13 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8416,7 +8408,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8434,7 +8426,7 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
@@ -8445,10 +8437,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8471,13 +8463,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8507,10 +8499,10 @@
         <v>114</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -8528,7 +8520,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8546,21 +8538,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8583,13 +8575,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8616,13 +8608,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -8640,7 +8632,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8658,21 +8650,21 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8695,19 +8687,19 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8732,13 +8724,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -8756,7 +8748,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8774,21 +8766,21 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8811,13 +8803,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8847,10 +8839,10 @@
         <v>114</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -8868,7 +8860,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8886,21 +8878,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8923,13 +8915,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8959,10 +8951,10 @@
         <v>114</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -8980,7 +8972,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8998,21 +8990,21 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9035,13 +9027,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9092,7 +9084,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9110,21 +9102,21 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9147,13 +9139,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9180,13 +9172,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9204,7 +9196,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9222,21 +9214,21 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9259,16 +9251,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9318,7 +9310,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9330,13 +9322,13 @@
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -9347,10 +9339,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9373,13 +9365,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9430,7 +9422,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9448,7 +9440,7 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -9459,14 +9451,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9488,13 +9480,13 @@
         <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9544,7 +9536,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9562,7 +9554,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -9573,14 +9565,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9602,16 +9594,16 @@
         <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9660,7 +9652,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9689,10 +9681,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9715,13 +9707,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9772,7 +9764,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>90</v>
@@ -9787,24 +9779,24 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9830,13 +9822,13 @@
         <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9862,13 +9854,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -9886,7 +9878,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9904,7 +9896,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -9915,10 +9907,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9941,16 +9933,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9976,13 +9968,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -10000,7 +9992,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10029,10 +10021,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10055,13 +10047,13 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10112,7 +10104,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10130,7 +10122,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10141,10 +10133,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10167,13 +10159,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10224,7 +10216,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10239,24 +10231,24 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10279,16 +10271,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10338,7 +10330,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10353,10 +10345,10 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-encounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -372,7 +372,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -467,7 +467,7 @@
     <t>associatedEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {encounter-associatedEncounter}
+    <t xml:space="preserve">Extension {encounter-associatedEncounter|4.0.1}
 </t>
   </si>
   <si>
@@ -656,13 +656,13 @@
 </t>
   </si>
   <si>
-    <t>患者とのEncounterの分類【詳細参照】</t>
+    <t>患者との受療行動の分類【詳細参照】</t>
   </si>
   <si>
     <t>外来（外来）、入院、救急、在宅医療、その他の地域差による患者Encounterの分類を表す概念。</t>
   </si>
   <si>
-    <t>コードは列挙やコードリストの中で非常にカジュアルに定義されることもあれば、SNOMED CTのような非常にフォーマルな定義まである。 - 詳細はHL7 v3コア・プリンシプルを参照すること。</t>
+    <t>コードは列挙やコードリストの中で非常にカジュアルに定義されることもあれば、SNOMED CTのような非常にフォーマルな定義まである。 - 詳細は[HL7 v3コア・プリンシプル](https://www.hl7.org/implement/standards/product_brief.cfm?product_id=481)を参照すること。</t>
   </si>
   <si>
     <t>extensible</t>
@@ -711,7 +711,7 @@
 入院｜外来｜外来｜救急＋。</t>
   </si>
   <si>
-    <t>コードは列挙やコードリストの中で非常にカジュアルに定義されることもあれば、SNOMED CTのような非常にフォーマルな定義まである- 詳細はHL7 v3コア・プリンシプルを参照すること。</t>
+    <t>コードは列挙やコードリストの中で非常にカジュアルに定義されることもあれば、SNOMED CTのような非常にフォーマルな定義まである- 詳細は[HL7 v3コア・プリンシプル](https://www.hl7.org/implement/standards/product_brief.cfm?product_id=481)を参照すること。</t>
   </si>
   <si>
     <t>Encounter.classHistory.period</t>
@@ -745,7 +745,7 @@
     <t>A specific code indicating type of service provided</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-type|4.3.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -769,7 +769,7 @@
     <t>Broad categorization of the service that is to be provided.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.3.0</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -831,7 +831,7 @@
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(EpisodeOfCare)
+    <t xml:space="preserve">Reference(EpisodeOfCare|4.3.0)
 </t>
   </si>
   <si>
@@ -857,7 +857,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.3.0)
 </t>
   </si>
   <si>
@@ -912,7 +912,7 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.3.0</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -967,7 +967,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment)
+    <t xml:space="preserve">Reference(Appointment|4.3.0)
 </t>
   </si>
   <si>
@@ -1048,7 +1048,7 @@
     <t>Reason why the encounter takes place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.3.0</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1066,7 +1066,7 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1101,7 +1101,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
 </t>
   </si>
   <si>
@@ -1132,7 +1132,7 @@
     <t>The type of diagnosis this condition represents.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnosis-role</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.3.0</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -1154,7 +1154,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account)
+    <t xml:space="preserve">Reference(Account|4.3.0)
 </t>
   </si>
   <si>
@@ -1236,7 +1236,7 @@
     <t>From where the patient was admitted.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.3.0</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -1281,7 +1281,7 @@
     <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.3.0</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
@@ -1302,7 +1302,7 @@
     <t>Special courtesies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.3.0</t>
   </si>
   <si>
     <t>.specialCourtesiesCode</t>
@@ -1323,7 +1323,7 @@
     <t>Special arrangements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.3.0</t>
   </si>
   <si>
     <t>.specialArrangementCode</t>
@@ -1359,7 +1359,7 @@
     <t>Discharge Disposition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition|4.3.0</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1451,7 +1451,7 @@
     <t>Physical form of the location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.3.0</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -1810,17 +1810,17 @@
   <dimension ref="A1:AN75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.67578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.2265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.16015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.16015625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.33984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="207.359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="230.390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1829,26 +1829,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="74.65625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.25390625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.67578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="64.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.75390625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="92.67578125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="191.1328125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="79.453125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="163.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="481">
   <si>
     <t>Property</t>
   </si>
@@ -467,11 +467,19 @@
     <t>associatedEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {encounter-associatedEncounter|4.0.1}
+    <t xml:space="preserve">Extension {encounter-associatedEncounter|4.3.0}
 </t>
   </si>
   <si>
     <t>関連するEncounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -2973,10 +2981,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -2993,14 +3001,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3022,16 +3030,16 @@
         <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -3080,7 +3088,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3109,10 +3117,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3135,13 +3143,13 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3192,7 +3200,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3207,24 +3215,24 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3250,13 +3258,13 @@
         <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3282,13 +3290,13 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -3306,7 +3314,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>90</v>
@@ -3321,24 +3329,24 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3361,16 +3369,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3420,7 +3428,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3432,13 +3440,13 @@
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
@@ -3449,10 +3457,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3475,13 +3483,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3532,7 +3540,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3550,7 +3558,7 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -3561,14 +3569,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3590,13 +3598,13 @@
         <v>136</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3646,7 +3654,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3664,7 +3672,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -3675,14 +3683,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3704,16 +3712,16 @@
         <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3762,7 +3770,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3791,10 +3799,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3820,13 +3828,13 @@
         <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3852,13 +3860,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -3876,7 +3884,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>90</v>
@@ -3894,7 +3902,7 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>81</v>
@@ -3905,10 +3913,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3931,16 +3939,16 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3990,7 +3998,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>90</v>
@@ -4008,7 +4016,7 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>81</v>
@@ -4019,10 +4027,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4045,16 +4053,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4080,13 +4088,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4104,7 +4112,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>90</v>
@@ -4122,21 +4130,21 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4159,13 +4167,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4216,7 +4224,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4228,13 +4236,13 @@
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
@@ -4245,10 +4253,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4271,13 +4279,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4328,7 +4336,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4346,7 +4354,7 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -4357,14 +4365,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4386,13 +4394,13 @@
         <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4442,7 +4450,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4460,7 +4468,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -4471,14 +4479,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4500,16 +4508,16 @@
         <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4558,7 +4566,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4587,10 +4595,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4613,16 +4621,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4648,13 +4656,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -4672,7 +4680,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>90</v>
@@ -4690,7 +4698,7 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -4701,10 +4709,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4727,16 +4735,16 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4786,7 +4794,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -4804,7 +4812,7 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
@@ -4815,10 +4823,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4841,16 +4849,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4876,13 +4884,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -4900,7 +4908,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4915,24 +4923,24 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4955,13 +4963,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4988,13 +4996,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -5012,7 +5020,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5027,24 +5035,24 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5067,13 +5075,13 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5100,31 +5108,31 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5142,25 +5150,25 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5179,16 +5187,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5238,7 +5246,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5253,24 +5261,24 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5293,13 +5301,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5350,7 +5358,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5365,28 +5373,28 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5405,13 +5413,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5462,7 +5470,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5477,10 +5485,10 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -5491,10 +5499,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5517,13 +5525,13 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5574,7 +5582,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5586,27 +5594,27 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5629,13 +5637,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5686,7 +5694,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5704,7 +5712,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -5715,14 +5723,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5744,13 +5752,13 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5800,7 +5808,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5818,7 +5826,7 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -5829,14 +5837,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5858,16 +5866,16 @@
         <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5916,7 +5924,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5945,10 +5953,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5971,16 +5979,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6006,31 +6014,31 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6045,24 +6053,24 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6085,13 +6093,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6142,7 +6150,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6160,21 +6168,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6197,13 +6205,13 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6254,7 +6262,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6269,24 +6277,24 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6309,13 +6317,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6366,7 +6374,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6381,24 +6389,24 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6421,16 +6429,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6480,7 +6488,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6495,24 +6503,24 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6535,16 +6543,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6594,7 +6602,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6609,28 +6617,28 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6649,16 +6657,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6687,10 +6695,10 @@
         <v>114</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -6708,7 +6716,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6723,28 +6731,28 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6763,16 +6771,16 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6822,7 +6830,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6837,24 +6845,24 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6877,13 +6885,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6934,7 +6942,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6946,13 +6954,13 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -6963,10 +6971,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6989,13 +6997,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7046,7 +7054,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7064,7 +7072,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7075,14 +7083,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7104,13 +7112,13 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7160,7 +7168,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7178,7 +7186,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7189,14 +7197,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7218,16 +7226,16 @@
         <v>136</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7276,7 +7284,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7305,14 +7313,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7331,16 +7339,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7390,7 +7398,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7405,24 +7413,24 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7445,13 +7453,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7481,10 +7489,10 @@
         <v>114</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7502,7 +7510,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7520,7 +7528,7 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -7531,10 +7539,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7557,13 +7565,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7614,7 +7622,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7632,7 +7640,7 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
@@ -7643,10 +7651,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7669,16 +7677,16 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7728,7 +7736,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7746,7 +7754,7 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7757,10 +7765,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7783,16 +7791,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7842,7 +7850,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7854,13 +7862,13 @@
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -7871,10 +7879,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7897,13 +7905,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7954,7 +7962,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7972,7 +7980,7 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -7983,14 +7991,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8012,13 +8020,13 @@
         <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8068,7 +8076,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8086,7 +8094,7 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
@@ -8097,14 +8105,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8126,16 +8134,16 @@
         <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8184,7 +8192,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8213,10 +8221,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8239,13 +8247,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8296,7 +8304,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8314,21 +8322,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8351,13 +8359,13 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8408,7 +8416,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8426,7 +8434,7 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
@@ -8437,10 +8445,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8463,13 +8471,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8499,10 +8507,10 @@
         <v>114</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -8520,7 +8528,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8538,21 +8546,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8575,13 +8583,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8608,13 +8616,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -8632,7 +8640,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8650,21 +8658,21 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8687,19 +8695,19 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8724,13 +8732,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -8748,7 +8756,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8766,21 +8774,21 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8803,13 +8811,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8839,10 +8847,10 @@
         <v>114</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -8860,7 +8868,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8878,21 +8886,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8915,13 +8923,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8951,10 +8959,10 @@
         <v>114</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -8972,7 +8980,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8990,21 +8998,21 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9027,13 +9035,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9084,7 +9092,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9102,21 +9110,21 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9139,13 +9147,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9172,13 +9180,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9196,7 +9204,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9214,21 +9222,21 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9251,16 +9259,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9310,7 +9318,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9322,13 +9330,13 @@
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -9339,10 +9347,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9365,13 +9373,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9422,7 +9430,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9440,7 +9448,7 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -9451,14 +9459,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9480,13 +9488,13 @@
         <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9536,7 +9544,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9554,7 +9562,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -9565,14 +9573,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9594,16 +9602,16 @@
         <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9652,7 +9660,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9681,10 +9689,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9707,13 +9715,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9764,7 +9772,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>90</v>
@@ -9779,24 +9787,24 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9822,13 +9830,13 @@
         <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9854,13 +9862,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -9878,7 +9886,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9896,7 +9904,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -9907,10 +9915,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9933,16 +9941,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9968,13 +9976,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -9992,7 +10000,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10021,10 +10029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10047,13 +10055,13 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10104,7 +10112,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10122,7 +10130,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10133,10 +10141,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10159,13 +10167,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10216,7 +10224,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10231,24 +10239,24 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10271,16 +10279,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10330,7 +10338,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10345,10 +10353,10 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-encounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-encounter.xlsx
@@ -273,8 +273,8 @@
 【JP Core仕様】外来受診、救急受診、入院、退院、対面診察、電話診察、など。</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -299,13 +299,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -318,16 +318,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -338,13 +338,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -357,19 +357,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>人間の言語。 / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -389,13 +389,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト要約 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -415,19 +415,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>含まれている、インラインのリソース / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -457,8 +457,8 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.extension:associatedEncounter</t>
@@ -478,8 +478,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -489,17 +489,17 @@
 user content</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>修飾子拡張により、安全に無視できない拡張を、安全に無視できる大多数の拡張と明確に区別することができます。これにより、実装者が拡張の存在を禁止する必要がなくなり、相互運用性が促進されます。詳細については、[修飾子拡張の定義](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension)を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -546,7 +546,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>Current state of the encounter.</t>
+    <t>受療行動の現状。 / Current state of the encounter.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-status|4.3.0</t>
@@ -580,7 +580,7 @@
     <t>現在のステータスは、ステータスの履歴ではなく、常にリソースの現在のバージョンにある。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -594,10 +594,10 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -606,10 +606,10 @@
     <t>Encounter.statusHistory.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -622,10 +622,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -676,7 +677,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>Classification of the encounter.</t>
+    <t>受療行動の分類。 / Classification of the encounter.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
@@ -738,19 +739,19 @@
 </t>
   </si>
   <si>
-    <t>Specific type of encounter</t>
-  </si>
-  <si>
-    <t>Specific type of encounter (e.g. e-mail consultation, surgical day-care, skilled nursing, rehabilitation).</t>
-  </si>
-  <si>
-    <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
+    <t>特定の種類の受療行動 / Specific type of encounter</t>
+  </si>
+  <si>
+    <t>特定の受療行動の種類（例：メール相談、手術日帰り、スキルド・ナーシング、リハビリテーション） / Specific type of encounter (e.g. e-mail consultation, surgical day-care, skilled nursing, rehabilitation).</t>
+  </si>
+  <si>
+    <t>受療行動をさらに分類する方法が多数存在するため、この要素は0から複数の値をとる。 / Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>A specific code indicating type of service provided</t>
+    <t>受療行動のタイプ。 / A specific code indicating type of service provided</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-type|4.3.0</t>
@@ -768,13 +769,13 @@
     <t>Encounter.serviceType</t>
   </si>
   <si>
-    <t>Specific type of service</t>
-  </si>
-  <si>
-    <t>Broad categorization of the service that is to be provided (e.g. cardiology).</t>
-  </si>
-  <si>
-    <t>Broad categorization of the service that is to be provided.</t>
+    <t>特定のサービスの種類 / Specific type of service</t>
+  </si>
+  <si>
+    <t>提供されるサービスの広範な分類（例：心臓病学） / Broad categorization of the service that is to be provided (e.g. cardiology).</t>
+  </si>
+  <si>
+    <t>提供されるサービスの広範な分類。 / Broad categorization of the service that is to be provided.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/service-type|4.3.0</t>
@@ -786,10 +787,10 @@
     <t>Encounter.priority</t>
   </si>
   <si>
-    <t>Indicates the urgency of the encounter</t>
-  </si>
-  <si>
-    <t>Indicates the urgency of the encounter.</t>
+    <t>受療行動の緊急性を示す / Indicates the urgency of the encounter</t>
+  </si>
+  <si>
+    <t>受療行動の緊急性を示します。 / Indicates the urgency of the encounter.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
@@ -815,13 +816,13 @@
 </t>
   </si>
   <si>
-    <t>The patient or group present at the encounter</t>
-  </si>
-  <si>
-    <t>The patient or group present at the encounter.</t>
-  </si>
-  <si>
-    <t>While the encounter is always about the patient, the patient might not actually be known in all contexts of use, and there may be a group of patients that could be anonymous (such as in a group therapy for Alcoholics Anonymous - where the recording of the encounter could be used for billing on the number of people/staff and not important to the context of the specific patients) or alternately in veterinary care a herd of sheep receiving treatment (where the animals are not individually tracked).</t>
+    <t>対面時に出席している患者またはグループ / The patient or group present at the encounter</t>
+  </si>
+  <si>
+    <t>診察時に存在する患者またはグループ。 / The patient or group present at the encounter.</t>
+  </si>
+  <si>
+    <t>エンカウンターは常に患者に関するものですが、すべての使用状況で患者が実際に知られていない場合があり、匿名である可能性があります（例えばアルコール依存症のグループセラピーの場合- エンカウンターの記録が人数/スタッフの請求に使用され、特定の患者の文脈に重要ではない場合、または獣医治療では、個々に追跡されていない群れの羊が治療を受ける場合があります）。 / While the encounter is always about the patient, the patient might not actually be known in all contexts of use, and there may be a group of patients that could be anonymous (such as in a group therapy for Alcoholics Anonymous - where the recording of the encounter could be used for billing on the number of people/staff and not important to the context of the specific patients) or alternately in veterinary care a herd of sheep receiving treatment (where the animals are not individually tracked).</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -843,10 +844,10 @@
 </t>
   </si>
   <si>
-    <t>Episode(s) of care that this encounter should be recorded against</t>
-  </si>
-  <si>
-    <t>Where a specific encounter should be classified as a part of a specific episode(s) of care this field should be used. This association can facilitate grouping of related encounters together for a specific purpose, such as government reporting, issue tracking, association via a common problem.  The association is recorded on the encounter as these are typically created after the episode of care and grouped on entry rather than editing the episode of care to append another encounter to it (the episode of care could span years).</t>
+    <t>このEnounterが記録されるべきケアのエピソード / Episode(s) of care that this encounter should be recorded against</t>
+  </si>
+  <si>
+    <t>特定のエピソードの一部として特定のエンカウンターを分類する必要がある場合、このフィールドを使用する必要があります。この関連は、政府報告、問題追跡、共通の課題に関連するエンカウンターを特定の目的のためにグループ化するのに役立ちます。これらの関連は、通常、エピソードの後に作成され、新しいエンカウンターを追加するためにエピソードを編集するのではなく、入力時にグループ化されます（エピソードは数年にわたって広がる可能性があります）。 / Where a specific encounter should be classified as a part of a specific episode(s) of care this field should be used. This association can facilitate grouping of related encounters together for a specific purpose, such as government reporting, issue tracking, association via a common problem.  The association is recorded on the encounter as these are typically created after the episode of care and grouped on entry rather than editing the episode of care to append another encounter to it (the episode of care could span years).</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -869,10 +870,10 @@
 </t>
   </si>
   <si>
-    <t>The ServiceRequest that initiated this encounter</t>
-  </si>
-  <si>
-    <t>The request this encounter satisfies (e.g. incoming referral or procedure request).</t>
+    <t>この受療行動を開始したサービスリクエスト / The ServiceRequest that initiated this encounter</t>
+  </si>
+  <si>
+    <t>この受療行動が満たす要請（例：紹介依頼や手続き要請） / The request this encounter satisfies (e.g. incoming referral or procedure request).</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -884,10 +885,10 @@
     <t>Encounter.participant</t>
   </si>
   <si>
-    <t>List of participants involved in the encounter</t>
-  </si>
-  <si>
-    <t>The list of people responsible for providing the service.</t>
+    <t>Enounterに関わった参加者のリスト / List of participants involved in the encounter</t>
+  </si>
+  <si>
+    <t>サービスを提供する責任を持つ人々のリスト / The list of people responsible for providing the service.</t>
   </si>
   <si>
     <t>Event.performer</t>
@@ -911,13 +912,13 @@
     <t>Encounter.participant.type</t>
   </si>
   <si>
-    <t>Role of participant in encounter</t>
-  </si>
-  <si>
-    <t>Role of participant in encounter.</t>
-  </si>
-  <si>
-    <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
+    <t>受療行動における参加者の役割 / Role of participant in encounter</t>
+  </si>
+  <si>
+    <t>受療行動における参加者の役割。 / Role of participant in encounter.</t>
+  </si>
+  <si>
+    <t>参加者タイプは、個人がどのようにエンカウントに参加するかを示します。それには、非開業者の参加者が含まれ、開業者にとってはこのエンカウントの文脈でアクションタイプを説明することが含まれます（例：入院医師、診療医師、翻訳者、相談医師）。これは、雇用、教育、免許などの用語から派生した機能的な役割である開業者の役割とは異なります。 / The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.3.0</t>
@@ -935,10 +936,10 @@
     <t>Encounter.participant.period</t>
   </si>
   <si>
-    <t>Period of time during the encounter that the participant participated</t>
-  </si>
-  <si>
-    <t>The period of time that the specified participant participated in the encounter. These can overlap or be sub-sets of the overall encounter's period.</t>
+    <t>参加者が参加したエンカウンターの期間 / Period of time during the encounter that the participant participated</t>
+  </si>
+  <si>
+    <t>指定された参加者が出席した期間。これらは重複することがあり、全体的なエンカウント期間のサブセットになることもあります。 / The period of time that the specified participant participated in the encounter. These can overlap or be sub-sets of the overall encounter's period.</t>
   </si>
   <si>
     <t>.time</t>
@@ -954,10 +955,10 @@
 </t>
   </si>
   <si>
-    <t>Persons involved in the encounter other than the patient</t>
-  </si>
-  <si>
-    <t>Persons involved in the encounter other than the patient.</t>
+    <t>患者以外に関与する人 / Persons involved in the encounter other than the patient</t>
+  </si>
+  <si>
+    <t>患者以外に受療行動に関わった人々。 / Persons involved in the encounter other than the patient.</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -979,10 +980,10 @@
 </t>
   </si>
   <si>
-    <t>The appointment that scheduled this encounter</t>
-  </si>
-  <si>
-    <t>The appointment that scheduled this encounter.</t>
+    <t>この受療行動を予定した予約 / The appointment that scheduled this encounter</t>
+  </si>
+  <si>
+    <t>この受療行動を予定した約束。 / The appointment that scheduled this encounter.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=FLFS].target[classCode=ENC, moodCode=APT]</t>
@@ -994,13 +995,13 @@
     <t>Encounter.period</t>
   </si>
   <si>
-    <t>The start and end time of the encounter</t>
-  </si>
-  <si>
-    <t>The start and end time of the encounter.</t>
-  </si>
-  <si>
-    <t>If not (yet) known, the end of the Period may be omitted.</t>
+    <t>受療行動の始まりと終わりの時間 / The start and end time of the encounter</t>
+  </si>
+  <si>
+    <t>受療行動の開始時刻と終了時刻。 / The start and end time of the encounter.</t>
+  </si>
+  <si>
+    <t>もし、まだ知られていなければ、期間の終わりは省略できます。 / If not (yet) known, the end of the Period may be omitted.</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1022,13 +1023,13 @@
 </t>
   </si>
   <si>
-    <t>Quantity of time the encounter lasted (less time absent)</t>
-  </si>
-  <si>
-    <t>Quantity of time the encounter lasted. This excludes the time during leaves of absence.</t>
-  </si>
-  <si>
-    <t>May differ from the time the Encounter.period lasted because of leave of absence.</t>
+    <t>受療行動が続いた時間（不在時間を差し引いた時間） / Quantity of time the encounter lasted (less time absent)</t>
+  </si>
+  <si>
+    <t>接触が続いた時間の量です。休暇中の時間は除かれます。 / Quantity of time the encounter lasted. This excludes the time during leaves of absence.</t>
+  </si>
+  <si>
+    <t>休暇により、エンカウンター期間の時間が異なる場合があります。 / May differ from the time the Encounter.period lasted because of leave of absence.</t>
   </si>
   <si>
     <t>.lengthOfStayQuantity</t>
@@ -1044,16 +1045,16 @@
 Admission diagnosis</t>
   </si>
   <si>
-    <t>Coded reason the encounter takes place</t>
-  </si>
-  <si>
-    <t>Reason the encounter takes place, expressed as a code. For admissions, this can be used for a coded admission diagnosis.</t>
-  </si>
-  <si>
-    <t>For systems that need to know which was the primary diagnosis, these will be marked with the standard extension primaryDiagnosis (which is a sequence value rather than a flag, 1 = primary diagnosis).</t>
-  </si>
-  <si>
-    <t>Reason why the encounter takes place.</t>
+    <t>エンカウントが生じる理由がコード化されている / Coded reason the encounter takes place</t>
+  </si>
+  <si>
+    <t>受療行動が起こる理由をコードとして表現します。入院に関しては、コード化された入院診断に使用できます。 / Reason the encounter takes place, expressed as a code. For admissions, this can be used for a coded admission diagnosis.</t>
+  </si>
+  <si>
+    <t>主要な診断を知る必要があるシステムには、標準拡張子primaryDiagnosis（フラグではなく、シーケンス値である1 = 主要な診断）でマークされます。 / For systems that need to know which was the primary diagnosis, these will be marked with the standard extension primaryDiagnosis (which is a sequence value rather than a flag, 1 = primary diagnosis).</t>
+  </si>
+  <si>
+    <t>受療行動が起こる理由。 / Reason why the encounter takes place.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.3.0</t>
@@ -1078,16 +1079,16 @@
 </t>
   </si>
   <si>
-    <t>Reason the encounter takes place (reference)</t>
+    <t>受療行動が生じた理由（参照） / Reason the encounter takes place (reference)</t>
   </si>
   <si>
     <t>Encounter.diagnosis</t>
   </si>
   <si>
-    <t>The list of diagnosis relevant to this encounter</t>
-  </si>
-  <si>
-    <t>The list of diagnosis relevant to this encounter.</t>
+    <t>この診察に関連する診断のリスト / The list of diagnosis relevant to this encounter</t>
+  </si>
+  <si>
+    <t>この対面に関連する診断リスト。 / The list of diagnosis relevant to this encounter.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=RSON]</t>
@@ -1113,10 +1114,10 @@
 </t>
   </si>
   <si>
-    <t>The diagnosis or procedure relevant to the encounter</t>
-  </si>
-  <si>
-    <t>Reason the encounter takes place, as specified using information from another resource. For admissions, this is the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
+    <t>エンカウンターに関連する診断または処置 / The diagnosis or procedure relevant to the encounter</t>
+  </si>
+  <si>
+    <t>エンカウンターが発生する理由は、他のリソースからの情報を使用して指定されます。入院の場合、これは入院診断です。指標は通常、状態（evidence.detailで参照される他のリソースで）またはプロシジャー（処置等）です。 / Reason the encounter takes place, as specified using information from another resource. For admissions, this is the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1131,13 +1132,13 @@
     <t>Encounter.diagnosis.use</t>
   </si>
   <si>
-    <t>Role that this diagnosis has within the encounter (e.g. admission, billing, discharge …)</t>
-  </si>
-  <si>
-    <t>Role that this diagnosis has within the encounter (e.g. admission, billing, discharge …).</t>
-  </si>
-  <si>
-    <t>The type of diagnosis this condition represents.</t>
+    <t>この診断に対する役割（入院、請求、退院など） / Role that this diagnosis has within the encounter (e.g. admission, billing, discharge …)</t>
+  </si>
+  <si>
+    <t>この診断が受療行動の中で果たす役割（入院、請求、退院など） / Role that this diagnosis has within the encounter (e.g. admission, billing, discharge …).</t>
+  </si>
+  <si>
+    <t>この状態が表す診断のタイプ。 / The type of diagnosis this condition represents.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.3.0</t>
@@ -1150,10 +1151,10 @@
 </t>
   </si>
   <si>
-    <t>Ranking of the diagnosis (for each role type)</t>
-  </si>
-  <si>
-    <t>Ranking of the diagnosis (for each role type).</t>
+    <t>役割ごとの診断ランキング / Ranking of the diagnosis (for each role type)</t>
+  </si>
+  <si>
+    <t>各役割タイプの診断ランキング / Ranking of the diagnosis (for each role type).</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=RSON].priority</t>
@@ -1166,13 +1167,13 @@
 </t>
   </si>
   <si>
-    <t>The set of accounts that may be used for billing for this Encounter</t>
-  </si>
-  <si>
-    <t>The set of accounts that may be used for billing for this Encounter.</t>
-  </si>
-  <si>
-    <t>The billing system may choose to allocate billable items associated with the Encounter to different referenced Accounts based on internal business rules.</t>
+    <t>このエンカウンターの請求に使用できるアカウントのセット / The set of accounts that may be used for billing for this Encounter</t>
+  </si>
+  <si>
+    <t>このエンカウンターの請求に使用できるアカウントのセット。 / The set of accounts that may be used for billing for this Encounter.</t>
+  </si>
+  <si>
+    <t>請求システムは内部のビジネスルールに基づいて、受療行動に関連する請求可能なアイテムを複数の参照されたアカウントに割り当てることができます。 / The billing system may choose to allocate billable items associated with the Encounter to different referenced Accounts based on internal business rules.</t>
   </si>
   <si>
     <t>.pertains.A_Account</t>
@@ -1181,13 +1182,14 @@
     <t>Encounter.hospitalization</t>
   </si>
   <si>
-    <t>Details about the admission to a healthcare service</t>
-  </si>
-  <si>
-    <t>Details about the admission to a healthcare service.</t>
-  </si>
-  <si>
-    <t>An Encounter may cover more than just the inpatient stay. Contexts such as outpatients, community clinics, and aged care facilities are also included.+    <t>医療サービスの入院に関する詳細 / Details about the admission to a healthcare service</t>
+  </si>
+  <si>
+    <t>医療サービスへの入院に関する詳細。 / Details about the admission to a healthcare service.</t>
+  </si>
+  <si>
+    <t>「エンカウンター」は入院期間だけでなく、外来診療、地域クリニック、高齢者施設などの文脈も含まれる場合があります。+この「エンカウンター」の期間に記録される期間は、この入院記録の全範囲をカバーしています。 / An Encounter may cover more than just the inpatient stay. Contexts such as outpatients, community clinics, and aged care facilities are also included.  The duration recorded in the period of this encounter covers the entire scope of this hospitalization record.</t>
   </si>
@@ -1207,10 +1209,10 @@
     <t>Encounter.hospitalization.preAdmissionIdentifier</t>
   </si>
   <si>
-    <t>Pre-admission identifier</t>
-  </si>
-  <si>
-    <t>Pre-admission identifier.</t>
+    <t>事前入院identifier / Pre-admission identifier</t>
+  </si>
+  <si>
+    <t>入院前のidentifier / Pre-admission identifier.</t>
   </si>
   <si>
     <t>PV1-5</t>
@@ -1223,10 +1225,10 @@
 </t>
   </si>
   <si>
-    <t>The location/organization from which the patient came before admission</t>
-  </si>
-  <si>
-    <t>The location/organization from which the patient came before admission.</t>
+    <t>入院前に患者がいた場所／組織 / The location/organization from which the patient came before admission</t>
+  </si>
+  <si>
+    <t>患者が入院する前に、どこの場所/組織から来たか。 / The location/organization from which the patient came before admission.</t>
   </si>
   <si>
     <t>.participation[typeCode=ORG].role</t>
@@ -1235,13 +1237,13 @@
     <t>Encounter.hospitalization.admitSource</t>
   </si>
   <si>
-    <t>From where patient was admitted (physician referral, transfer)</t>
-  </si>
-  <si>
-    <t>From where patient was admitted (physician referral, transfer).</t>
-  </si>
-  <si>
-    <t>From where the patient was admitted.</t>
+    <t>患者が入院した場所（医師の紹介、転院） / From where patient was admitted (physician referral, transfer)</t>
+  </si>
+  <si>
+    <t>患者がどこから入院したのか（医師の紹介、転院） / From where patient was admitted (physician referral, transfer).</t>
+  </si>
+  <si>
+    <t>患者が入院した場所はどこですか。 / From where the patient was admitted.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.3.0</t>
@@ -1256,13 +1258,13 @@
     <t>Encounter.hospitalization.reAdmission</t>
   </si>
   <si>
-    <t>The type of hospital re-admission that has occurred (if any). If the value is absent, then this is not identified as a readmission</t>
-  </si>
-  <si>
-    <t>Whether this hospitalization is a readmission and why if known.</t>
-  </si>
-  <si>
-    <t>The reason for re-admission of this hospitalization encounter.</t>
+    <t>発生した再入院のタイプ（あれば）。値がない場合は、再入院として識別されていないことを意味します。 / The type of hospital re-admission that has occurred (if any). If the value is absent, then this is not identified as a readmission</t>
+  </si>
+  <si>
+    <t>この入院が再入院かどうか、そしてその理由が分かっている場合はなぜか。 / Whether this hospitalization is a readmission and why if known.</t>
+  </si>
+  <si>
+    <t>この入院の再入院の理由。 / The reason for re-admission of this hospitalization encounter.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
@@ -1274,19 +1276,19 @@
     <t>Encounter.hospitalization.dietPreference</t>
   </si>
   <si>
-    <t>Diet preferences reported by the patient</t>
-  </si>
-  <si>
-    <t>Diet preferences reported by the patient.</t>
-  </si>
-  <si>
-    <t>For example, a patient may request both a dairy-free and nut-free diet preference (not mutually exclusive).</t>
-  </si>
-  <si>
-    <t>Used to track patient's diet restrictions and/or preference. For a complete description of the nutrition needs of a patient during their stay, one should use the nutritionOrder resource which links to Encounter.</t>
-  </si>
-  <si>
-    <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
+    <t>患者が報告した食事の好み / Diet preferences reported by the patient</t>
+  </si>
+  <si>
+    <t>患者が報告した食事の好み。 / Diet preferences reported by the patient.</t>
+  </si>
+  <si>
+    <t>例えば、患者が乳製品フリーとナッツフリーの食事を希望することがあります（相反する要素ではありません）。 / For example, a patient may request both a dairy-free and nut-free diet preference (not mutually exclusive).</t>
+  </si>
+  <si>
+    <t>患者の食事制限および/または嗜好を追跡するために使用される。滞在中の患者の栄養ニーズの完全な記述には、Encounterにリンクする nutritionOrder リソースを使用すべきである。 / Used to track patient's diet restrictions and/or preference. For a complete description of the nutrition needs of a patient during their stay, one should use the nutritionOrder resource which links to Encounter.</t>
+  </si>
+  <si>
+    <t>食品の好みを考慮して、医療、文化、倫理的観点から、提供要件に対応することができます。 / Medical, cultural or ethical food preferences to help with catering requirements.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.3.0</t>
@@ -1301,13 +1303,13 @@
     <t>Encounter.hospitalization.specialCourtesy</t>
   </si>
   <si>
-    <t>Special courtesies (VIP, board member)</t>
-  </si>
-  <si>
-    <t>Special courtesies (VIP, board member).</t>
-  </si>
-  <si>
-    <t>Special courtesies.</t>
+    <t>特別な配慮（VIP、取締役） / Special courtesies (VIP, board member)</t>
+  </si>
+  <si>
+    <t>特別なおもてなし（VIP、取締役） / Special courtesies (VIP, board member).</t>
+  </si>
+  <si>
+    <t>特別なおもてなし。 / Special courtesies.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.3.0</t>
@@ -1322,13 +1324,13 @@
     <t>Encounter.hospitalization.specialArrangement</t>
   </si>
   <si>
-    <t>Wheelchair, translator, stretcher, etc.</t>
-  </si>
-  <si>
-    <t>Any special requests that have been made for this hospitalization encounter, such as the provision of specific equipment or other things.</t>
-  </si>
-  <si>
-    <t>Special arrangements.</t>
+    <t>車椅子、翻訳者、ストレッチャー、など。 / Wheelchair, translator, stretcher, etc.</t>
+  </si>
+  <si>
+    <t>この入院の機会に行われた特別な要求、特定の装置などの提供などがある場合は。 / Any special requests that have been made for this hospitalization encounter, such as the provision of specific equipment or other things.</t>
+  </si>
+  <si>
+    <t>特別な手配。 / Special arrangements.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.3.0</t>
@@ -1343,10 +1345,10 @@
     <t>Encounter.hospitalization.destination</t>
   </si>
   <si>
-    <t>Location/organization to which the patient is discharged</t>
-  </si>
-  <si>
-    <t>Location/organization to which the patient is discharged.</t>
+    <t>患者が退院する場所/施設 / Location/organization to which the patient is discharged</t>
+  </si>
+  <si>
+    <t>患者が退院する場所/組織。 / Location/organization to which the patient is discharged.</t>
   </si>
   <si>
     <t>.participation[typeCode=DST]</t>
@@ -1358,13 +1360,13 @@
     <t>Encounter.hospitalization.dischargeDisposition</t>
   </si>
   <si>
-    <t>Category or kind of location after discharge</t>
-  </si>
-  <si>
-    <t>Category or kind of location after discharge.</t>
-  </si>
-  <si>
-    <t>Discharge Disposition.</t>
+    <t>退院後の場所のカテゴリーまたは種類 / Category or kind of location after discharge</t>
+  </si>
+  <si>
+    <t>退院後の場所のカテゴリーまたは種類。 / Category or kind of location after discharge.</t>
+  </si>
+  <si>
+    <t>退院時の配慮。 / Discharge Disposition.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition|4.3.0</t>
@@ -1379,13 +1381,13 @@
     <t>Encounter.location</t>
   </si>
   <si>
-    <t>List of locations where the patient has been</t>
-  </si>
-  <si>
-    <t>List of locations where  the patient has been during this encounter.</t>
-  </si>
-  <si>
-    <t>Virtual encounters can be recorded in the Encounter by specifying a location reference to a location of type "kind" such as "client's home" and an encounter.class = "virtual".</t>
+    <t>患者が行った場所のリスト / List of locations where the patient has been</t>
+  </si>
+  <si>
+    <t>この接触中に患者が滞在した場所のリスト / List of locations where  the patient has been during this encounter.</t>
+  </si>
+  <si>
+    <t>エンカウント」には、場所の種類である「クライアントの自宅」のような場所の参照を明示することで、バーチャルなエンカウントを記録できます。また、エンカウントクラスは「バーチャル」である必要があります。 / Virtual encounters can be recorded in the Encounter by specifying a location reference to a location of type "kind" such as "client's home" and an encounter.class = "virtual".</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC]</t>
@@ -1407,10 +1409,10 @@
 </t>
   </si>
   <si>
-    <t>Location the encounter takes place</t>
-  </si>
-  <si>
-    <t>The location where the encounter takes place.</t>
+    <t>受療行動の場所 / Location the encounter takes place</t>
+  </si>
+  <si>
+    <t>受療行動が起こる場所。 / The location where the encounter takes place.</t>
   </si>
   <si>
     <t>Event.location</t>
@@ -1425,16 +1427,16 @@
     <t>Encounter.location.status</t>
   </si>
   <si>
-    <t>planned | active | reserved | completed</t>
-  </si>
-  <si>
-    <t>The status of the participants' presence at the specified location during the period specified. If the participant is no longer at the location, then the period will have an end date/time.</t>
-  </si>
-  <si>
-    <t>When the patient is no longer active at a location, then the period end date is entered, and the status may be changed to completed.</t>
-  </si>
-  <si>
-    <t>The status of the location.</t>
+    <t>計画中 | アクティブな | 予約済みの | 完了しました。 / planned | active | reserved | completed</t>
+  </si>
+  <si>
+    <t>指定された場所に参加者が期間中にいる状態。参加者が場所にいなくなった場合は、期間に終了日時が設定されます。 / The status of the participants' presence at the specified location during the period specified. If the participant is no longer at the location, then the period will have an end date/time.</t>
+  </si>
+  <si>
+    <t>患者が場所でのアクティブな期間が終了したら、期間終了日が入力され、ステータスが完了に変更される場合があります。 / When the patient is no longer active at a location, then the period end date is entered, and the status may be changed to completed.</t>
+  </si>
+  <si>
+    <t>場所の状態。 / The status of the location.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-location-status|4.3.0</t>
@@ -1446,17 +1448,18 @@
     <t>Encounter.location.physicalType</t>
   </si>
   <si>
-    <t>The physical type of the location (usually the level in the location hierachy - bed room ward etc.)</t>
-  </si>
-  <si>
-    <t>This will be used to specify the required levels (bed/ward/room/etc.) desired to be recorded to simplify either messaging or query.</t>
-  </si>
-  <si>
-    <t>This information is de-normalized from the Location resource to support the easier understanding of the encounter resource and processing in messaging or query.
+    <t>場所の物理的なタイプ（通常は場所の階層のレベル、ベッドルームワードなど） / The physical type of the location (usually the level in the location hierachy - bed room ward etc.)</t>
+  </si>
+  <si>
+    <t>これは、メッセージングまたはクエリを簡素化するために記録が必要なレベル（ベッド/病室/部屋など）を特定するために使用されます。 / This will be used to specify the required levels (bed/ward/room/etc.) desired to be recorded to simplify either messaging or query.</t>
+  </si>
+  <si>
+    <t>この情報は、エンカウンターリソースの理解とメッセージングまたはクエリの処理をサポートするために、ロケーションリソースからデノーマライズされています。
+階層には多くのレベルがあり、特定の使用シナリオに必要な特定のレベルのみをピックアップすることができます。 / This information is de-normalized from the Location resource to support the easier understanding of the encounter resource and processing in messaging or query.
 There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
   </si>
   <si>
-    <t>Physical form of the location.</t>
+    <t>場所の実体形態。 / Physical form of the location.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.3.0</t>
@@ -1465,10 +1468,10 @@
     <t>Encounter.location.period</t>
   </si>
   <si>
-    <t>Time period during which the patient was present at the location</t>
-  </si>
-  <si>
-    <t>Time period during which the patient was present at the location.</t>
+    <t>患者が場所にいた期間 / Time period during which the patient was present at the location</t>
+  </si>
+  <si>
+    <t>患者が場所にいた期間。 / Time period during which the patient was present at the location.</t>
   </si>
   <si>
     <t>Encounter.serviceProvider</t>
@@ -1478,10 +1481,10 @@
 </t>
   </si>
   <si>
-    <t>The organization (facility) responsible for this encounter</t>
-  </si>
-  <si>
-    <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
+    <t>この受療行動に責任を持つ組織（施設） / The organization (facility) responsible for this encounter</t>
+  </si>
+  <si>
+    <t>このエンカウンターのサービスを主に担当する組織。これは患者の記録にある組織と同じかもしれませんが、外部組織からサービスを提供するアクターがいる場合など、別の組織である可能性もあります(別途請求される可能性があります)。大腸内視鏡検査の簡略化されたエンカウンターのBundleを参照してください。 / The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
   </si>
   <si>
     <t>.particiaption[typeCode=PFM].role</t>
@@ -1497,13 +1500,13 @@
 </t>
   </si>
   <si>
-    <t>Another Encounter this encounter is part of</t>
-  </si>
-  <si>
-    <t>Another Encounter of which this encounter is a part of (administratively or in time).</t>
-  </si>
-  <si>
-    <t>This is also used for associating a child's encounter back to the mother's encounter.+    <t>もう一度の受療行動。この受療行動は一部である。 / Another Encounter this encounter is part of</t>
+  </si>
+  <si>
+    <t>この受療行動が一部である、別の受療行動（手続き的にも時間的にも）。 / Another Encounter of which this encounter is a part of (administratively or in time).</t>
+  </si>
+  <si>
+    <t>これは、子供の経験を母親の経験に関連付けるためにも使用されます。詳細については、患者リソースのノートセクションを参照してください。 / This is also used for associating a child's encounter back to the mother's encounter.  Refer to the Notes section in the Patient resource for further details.</t>
   </si>
@@ -1842,7 +1845,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="64.00390625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="105.1484375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.75390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
